--- a/registration_forms/047_hub_city_showcase--registration_forms.xlsx
+++ b/registration_forms/047_hub_city_showcase--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1499,29 +1499,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>blonde</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blonde</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>player_haircolor_choices</t>
+          <t>player_eyecolor_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>brown</t>
+          <t>hazel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Hazel</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hazel</t>
+          <t>amber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>Amber</t>
         </is>
       </c>
     </row>
@@ -1601,29 +1601,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>amber</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>player_eyecolor_choices</t>
+          <t>player_height_unit_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>ft</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>in</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>cm</t>
         </is>
       </c>
     </row>
@@ -1669,29 +1669,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>player_height_unit_choices</t>
+          <t>player_weight_unit_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>lbs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>lbs</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lbs</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>lbs</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>oz</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>oz</t>
         </is>
       </c>
     </row>
@@ -1737,29 +1737,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>stone</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>player_weight_unit_choices</t>
+          <t>player_tshirt_size_unit_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>stone</t>
+          <t>xs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>stone</t>
+          <t>xs</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>xs</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>xs</t>
+          <t>s</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
     </row>
@@ -1822,29 +1822,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>xl</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>player_tshirt_size_unit_choices</t>
+          <t>player_shoes_size_unit_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>xl</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>xl</t>
+          <t>in</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>cm</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>uk</t>
         </is>
       </c>
     </row>
@@ -1890,29 +1890,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>us</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>player_shoes_size_unit_choices</t>
+          <t>player_haircut_unit_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>in</t>
         </is>
       </c>
     </row>
@@ -1924,27 +1924,10 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>player_haircut_unit_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ft</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
         <is>
           <t>ft</t>
         </is>
